--- a/output/roomself_excel/11304.xlsx
+++ b/output/roomself_excel/11304.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:AB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,122 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_8</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_8</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_8</t>
         </is>
       </c>
     </row>
@@ -475,11 +585,93 @@
       <c r="D2" t="n">
         <v>6716</v>
       </c>
-      <c r="E2" t="n">
-        <v>849</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>668</v>
+        <v>740</v>
+      </c>
+      <c r="G2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>439</v>
+      </c>
+      <c r="J2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>204</v>
+      </c>
+      <c r="M2" t="n">
+        <v>18</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>49</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>200</v>
+      </c>
+      <c r="S2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>164</v>
+      </c>
+      <c r="V2" t="n">
+        <v>22</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>692</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +689,46 @@
       <c r="D3" t="n">
         <v>1352</v>
       </c>
-      <c r="E3" t="n">
-        <v>180</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
+        <v>124</v>
+      </c>
+      <c r="G3" t="n">
         <v>37</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>56</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/11304.xlsx
+++ b/output/roomself_excel/11304.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,86 @@
           <t>ExtWallWidth_8</t>
         </is>
       </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -671,6 +751,70 @@
         <v>95</v>
       </c>
       <c r="AB2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>256</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>199</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>157</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>87</v>
+      </c>
+      <c r="AR2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -729,6 +873,22 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
